--- a/Thesis_TSSP_NEW_M1_Results_5_Scenarios.xlsx
+++ b/Thesis_TSSP_NEW_M1_Results_5_Scenarios.xlsx
@@ -468,7 +468,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>4/5/2026 16:05</t>
+          <t>4/5/2026 15:45</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -478,7 +478,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>4/5/2026 16:05</t>
+          <t>4/5/2026 15:45</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -488,7 +488,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>4/5/2026 16:05</t>
+          <t>4/5/2026 15:45</t>
         </is>
       </c>
     </row>
@@ -500,22 +500,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Unload Gate 4</t>
+          <t>Unload Gate 2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>4/5/2026 16:05</t>
+          <t>4/5/2026 15:45</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Transport Cart 3</t>
+          <t>Transport Cart 2</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>4/5/2026 16:05</t>
+          <t>4/5/2026 15:45</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>4/5/2026 16:05</t>
+          <t>4/5/2026 15:45</t>
         </is>
       </c>
     </row>
@@ -542,17 +542,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4/5/2026 16:05</t>
+          <t>4/5/2026 15:45</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Transport Cart 2</t>
+          <t>Transport Cart 1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>4/5/2026 16:05</t>
+          <t>4/5/2026 15:45</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -562,7 +562,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>4/5/2026 16:05</t>
+          <t>4/5/2026 15:45</t>
         </is>
       </c>
     </row>
@@ -574,32 +574,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Unload Gate 2</t>
+          <t>Unload Gate 3</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>4/5/2026 16:05</t>
+          <t>4/5/2026 15:45</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Transport Cart 1</t>
+          <t>Transport Cart 3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>4/5/2026 08:59</t>
+          <t>4/5/2026 09:01</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Infeed Station 1</t>
+          <t>Infeed Station 2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>4/5/2026 09:04</t>
+          <t>4/5/2026 15:45</t>
         </is>
       </c>
     </row>
@@ -611,32 +611,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Unload Gate 1</t>
+          <t>Unload Gate 2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4/5/2026 16:05</t>
+          <t>4/5/2026 15:45</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Transport Cart 2</t>
+          <t>Transport Cart 1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>4/5/2026 16:05</t>
+          <t>4/5/2026 15:45</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Infeed Station 2</t>
+          <t>Infeed Station 1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>4/5/2026 16:05</t>
+          <t>4/5/2026 15:45</t>
         </is>
       </c>
     </row>
@@ -648,32 +648,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Unload Gate 1</t>
+          <t>Unload Gate 2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>4/5/2026 08:06</t>
+          <t>4/5/2026 07:19</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Transport Cart 3</t>
+          <t>Transport Cart 2</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>4/5/2026 07:19</t>
+          <t>4/5/2026 07:44</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Infeed Station 3</t>
+          <t>Infeed Station 1</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>4/5/2026 07:19</t>
+          <t>4/5/2026 08:04</t>
         </is>
       </c>
     </row>
@@ -690,27 +690,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>4/5/2026 16:05</t>
+          <t>4/5/2026 06:48</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Transport Cart 3</t>
+          <t>Transport Cart 2</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>4/5/2026 07:35</t>
+          <t>4/5/2026 07:16</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Infeed Station 2</t>
+          <t>Infeed Station 1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>4/5/2026 06:49</t>
+          <t>4/5/2026 07:00</t>
         </is>
       </c>
     </row>
@@ -722,12 +722,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Unload Gate 3</t>
+          <t>Unload Gate 2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>4/5/2026 09:21</t>
+          <t>4/5/2026 10:38</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -737,17 +737,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>4/5/2026 11:12</t>
+          <t>4/5/2026 12:00</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Infeed Station 2</t>
+          <t>Infeed Station 1</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>4/5/2026 09:21</t>
+          <t>4/5/2026 11:17</t>
         </is>
       </c>
     </row>
@@ -759,32 +759,32 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Unload Gate 3</t>
+          <t>Unload Gate 2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>4/5/2026 08:27</t>
+          <t>4/5/2026 10:31</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Transport Cart 1</t>
+          <t>Transport Cart 2</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>4/5/2026 10:26</t>
+          <t>4/5/2026 08:28</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Infeed Station 2</t>
+          <t>Infeed Station 1</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>4/5/2026 12:35</t>
+          <t>4/5/2026 09:44</t>
         </is>
       </c>
     </row>
@@ -796,12 +796,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Unload Gate 4</t>
+          <t>Unload Gate 3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>4/5/2026 07:26</t>
+          <t>4/5/2026 10:02</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>4/5/2026 10:56</t>
+          <t>4/5/2026 12:39</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -821,7 +821,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>4/5/2026 07:26</t>
+          <t>4/5/2026 15:45</t>
         </is>
       </c>
     </row>
@@ -833,24 +833,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Unload Gate 2</t>
+          <t>Unload Gate 4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>4/5/2026 08:05</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Transport Cart 2</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>4/5/2026 08:06</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Transport Cart 2</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>4/5/2026 08:05</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>Infeed Station 1</t>
@@ -858,7 +858,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>4/5/2026 08:41</t>
+          <t>4/5/2026 15:41</t>
         </is>
       </c>
     </row>
@@ -870,22 +870,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Unload Gate 3</t>
+          <t>Unload Gate 4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>4/5/2026 15:59</t>
+          <t>4/5/2026 10:12</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Transport Cart 3</t>
+          <t>Transport Cart 2</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>4/5/2026 16:05</t>
+          <t>4/5/2026 08:32</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>4/5/2026 10:24</t>
+          <t>4/5/2026 09:23</t>
         </is>
       </c>
     </row>
@@ -907,22 +907,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Unload Gate 3</t>
+          <t>Unload Gate 2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>4/5/2026 14:30</t>
+          <t>4/5/2026 08:47</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Transport Cart 1</t>
+          <t>Transport Cart 3</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>4/5/2026 16:04</t>
+          <t>4/5/2026 14:28</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>4/5/2026 14:47</t>
+          <t>4/5/2026 12:36</t>
         </is>
       </c>
     </row>
@@ -949,27 +949,27 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>4/5/2026 10:54</t>
+          <t>4/5/2026 15:41</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Transport Cart 1</t>
+          <t>Transport Cart 2</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>4/5/2026 06:30</t>
+          <t>4/5/2026 07:25</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Infeed Station 2</t>
+          <t>Infeed Station 3</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>4/5/2026 15:51</t>
+          <t>4/5/2026 08:03</t>
         </is>
       </c>
     </row>
@@ -981,32 +981,32 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Unload Gate 4</t>
+          <t>Unload Gate 3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>4/5/2026 07:09</t>
+          <t>4/5/2026 15:37</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Transport Cart 2</t>
+          <t>Transport Cart 3</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>4/5/2026 14:12</t>
+          <t>4/5/2026 08:23</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Infeed Station 3</t>
+          <t>Infeed Station 2</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>4/5/2026 07:08</t>
+          <t>4/5/2026 13:46</t>
         </is>
       </c>
     </row>
@@ -1018,32 +1018,32 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Unload Gate 3</t>
+          <t>Unload Gate 4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>4/5/2026 10:39</t>
+          <t>4/5/2026 12:34</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Transport Cart 1</t>
+          <t>Transport Cart 2</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>4/5/2026 13:03</t>
+          <t>4/5/2026 14:58</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Infeed Station 2</t>
+          <t>Infeed Station 3</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>4/5/2026 09:11</t>
+          <t>4/5/2026 15:42</t>
         </is>
       </c>
     </row>
@@ -1055,32 +1055,32 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Unload Gate 4</t>
+          <t>Unload Gate 3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>4/5/2026 12:51</t>
+          <t>4/5/2026 09:46</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Transport Cart 3</t>
+          <t>Transport Cart 2</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>4/5/2026 13:35</t>
+          <t>4/5/2026 15:29</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Infeed Station 3</t>
+          <t>Infeed Station 1</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>4/5/2026 12:59</t>
+          <t>4/5/2026 09:35</t>
         </is>
       </c>
     </row>
@@ -1097,27 +1097,27 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>4/5/2026 09:54</t>
+          <t>4/5/2026 13:59</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Transport Cart 1</t>
+          <t>Transport Cart 2</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>4/5/2026 12:28</t>
+          <t>4/5/2026 15:43</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Infeed Station 3</t>
+          <t>Infeed Station 2</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>4/5/2026 14:48</t>
+          <t>4/5/2026 09:17</t>
         </is>
       </c>
     </row>
@@ -1129,12 +1129,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Unload Gate 2</t>
+          <t>Unload Gate 4</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>4/5/2026 16:05</t>
+          <t>4/5/2026 12:21</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1144,17 +1144,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>4/5/2026 09:52</t>
+          <t>4/5/2026 08:46</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Infeed Station 1</t>
+          <t>Infeed Station 2</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>4/5/2026 14:59</t>
+          <t>4/5/2026 09:10</t>
         </is>
       </c>
     </row>
@@ -1171,7 +1171,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>4/5/2026 10:08</t>
+          <t>4/5/2026 09:01</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>4/5/2026 14:27</t>
+          <t>4/5/2026 15:14</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>4/5/2026 12:16</t>
+          <t>4/5/2026 12:40</t>
         </is>
       </c>
     </row>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>4/5/2026 15:16</t>
+          <t>4/5/2026 13:45</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>4/5/2026 14:45</t>
+          <t>4/5/2026 08:56</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>4/5/2026 16:05</t>
+          <t>4/5/2026 09:01</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>421.20 min</t>
+          <t>436.20 min</t>
         </is>
       </c>
     </row>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>32.24 min</t>
+          <t>34.88 min</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>89.40 min</t>
+          <t>86.60 min</t>
         </is>
       </c>
     </row>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>108.00 min</t>
+          <t>93.00 min</t>
         </is>
       </c>
     </row>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>20.00 min</t>
+          <t>29.60 min</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3.60/6.00/11.40 min</t>
+          <t>14.20/10.00/12.60 min</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>593073 / 32736</t>
+          <t>567873 / 31736</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>17.9020 sec</t>
+          <t>21.2800 sec</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0.2982 %</t>
+          <t>1.4136 %</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
@@ -1457,7 +1457,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>36.29 min | 108.00 min</t>
+          <t>35.90 min | 93.00 min</t>
         </is>
       </c>
     </row>
@@ -1514,7 +1514,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>29.62 min | 86.00 min</t>
+          <t>34.95 min | 86.00 min</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>30.43 min | 83.00 min</t>
+          <t>33.38 min | 83.00 min</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>32.33 min | 82.00 min</t>
+          <t>36.57 min | 82.00 min</t>
         </is>
       </c>
     </row>
@@ -1550,7 +1550,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>32.52 min | 88.00 min</t>
+          <t>33.57 min | 89.00 min</t>
         </is>
       </c>
     </row>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>11.66</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="36">
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>9.32</v>
+        <v>15.76</v>
       </c>
     </row>
     <row r="37">
@@ -1597,7 +1597,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>16.32</v>
+        <v>13.51</v>
       </c>
     </row>
     <row r="38">
@@ -1607,7 +1607,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>11.66</v>
+        <v>11.26</v>
       </c>
     </row>
     <row r="39">
@@ -1617,7 +1617,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4.09</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="40">
@@ -1627,7 +1627,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>2.27</v>
+        <v>4.83</v>
       </c>
     </row>
     <row r="41">
@@ -1637,7 +1637,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>3.18</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="42">
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>27.09</v>
+        <v>43.6</v>
       </c>
     </row>
     <row r="43">
@@ -1657,7 +1657,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>36.12</v>
+        <v>26.16</v>
       </c>
     </row>
     <row r="44">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>31.61</v>
+        <v>21.8</v>
       </c>
     </row>
   </sheetData>
@@ -1772,48 +1772,48 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>4/5/2026 08:52</t>
+          <t>4/5/2026 08:51</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>4/5/2026 09:03</t>
+          <t>4/5/2026 09:02</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>4/5/2026 09:03</t>
+          <t>4/5/2026 09:12</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>4/5/2026 09:05</t>
+          <t>4/5/2026 09:14</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>4/5/2026 09:08</t>
+          <t>4/5/2026 09:22</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>4/5/2026 10:01</t>
+          <t>4/5/2026 10:15</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="M2" t="n">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="N2" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3">
@@ -1832,25 +1832,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>4/5/2026 09:21</t>
+          <t>4/5/2026 09:13</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>4/5/2026 09:48</t>
+          <t>4/5/2026 09:40</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>4/5/2026 09:48</t>
+          <t>4/5/2026 09:40</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>4/5/2026 09:50</t>
+          <t>4/5/2026 09:42</t>
         </is>
       </c>
       <c r="I3" t="n">
@@ -1858,22 +1858,22 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>4/5/2026 09:57</t>
+          <t>4/5/2026 09:42</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>4/5/2026 11:01</t>
+          <t>4/5/2026 10:46</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="N3" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -1892,25 +1892,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4/5/2026 12:48</t>
+          <t>4/5/2026 12:53</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>4/5/2026 13:00</t>
+          <t>4/5/2026 13:05</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>4/5/2026 13:00</t>
+          <t>4/5/2026 13:05</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>4/5/2026 13:02</t>
+          <t>4/5/2026 13:07</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -1918,22 +1918,22 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>4/5/2026 13:02</t>
+          <t>4/5/2026 13:07</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>4/5/2026 13:09</t>
+          <t>4/5/2026 13:14</t>
         </is>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -2038,22 +2038,22 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>4/5/2026 09:12</t>
+          <t>4/5/2026 09:13</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>4/5/2026 09:13</t>
+          <t>4/5/2026 09:14</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -2372,25 +2372,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>4/5/2026 11:41</t>
+          <t>4/5/2026 11:56</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>4/5/2026 11:51</t>
+          <t>4/5/2026 12:06</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>4/5/2026 11:51</t>
+          <t>4/5/2026 12:06</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>4/5/2026 11:52</t>
+          <t>4/5/2026 12:07</t>
         </is>
       </c>
       <c r="I12" t="n">
@@ -2398,22 +2398,22 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>4/5/2026 11:52</t>
+          <t>4/5/2026 12:16</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>4/5/2026 11:58</t>
+          <t>4/5/2026 12:22</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M12" t="n">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13">
@@ -2638,22 +2638,22 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>4/5/2026 08:39</t>
+          <t>4/5/2026 08:42</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>4/5/2026 08:47</t>
+          <t>4/5/2026 08:50</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M16" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -2758,22 +2758,22 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>4/5/2026 09:17</t>
+          <t>4/5/2026 09:14</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>4/5/2026 09:25</t>
+          <t>4/5/2026 09:22</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M18" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="N18" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -2912,48 +2912,48 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>4/5/2026 08:37</t>
+          <t>4/5/2026 08:32</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>4/5/2026 08:51</t>
+          <t>4/5/2026 08:46</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>4/5/2026 09:11</t>
+          <t>4/5/2026 08:46</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>4/5/2026 09:15</t>
+          <t>4/5/2026 08:50</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>4/5/2026 09:32</t>
+          <t>4/5/2026 08:50</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>4/5/2026 10:05</t>
+          <t>4/5/2026 09:23</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>93</v>
+        <v>51</v>
       </c>
       <c r="N21" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2998,22 +2998,22 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>4/5/2026 09:05</t>
+          <t>4/5/2026 09:10</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>4/5/2026 09:08</t>
+          <t>4/5/2026 09:13</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M22" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23">
@@ -3152,48 +3152,48 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>4/5/2026 12:48</t>
+          <t>4/5/2026 13:03</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>4/5/2026 12:57</t>
+          <t>4/5/2026 13:12</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>4/5/2026 12:57</t>
+          <t>4/5/2026 13:21</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>4/5/2026 13:00</t>
+          <t>4/5/2026 13:24</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>4/5/2026 13:00</t>
+          <t>4/5/2026 13:24</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>4/5/2026 13:07</t>
+          <t>4/5/2026 13:31</t>
         </is>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="26">
@@ -3212,25 +3212,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>4/5/2026 09:53</t>
+          <t>4/5/2026 10:05</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>4/5/2026 09:55</t>
+          <t>4/5/2026 10:07</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>4/5/2026 09:55</t>
+          <t>4/5/2026 10:07</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>4/5/2026 09:57</t>
+          <t>4/5/2026 10:09</t>
         </is>
       </c>
       <c r="I26" t="n">
@@ -3238,22 +3238,22 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>4/5/2026 09:57</t>
+          <t>4/5/2026 10:09</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>4/5/2026 10:04</t>
+          <t>4/5/2026 10:16</t>
         </is>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="27">
@@ -3478,22 +3478,22 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>4/5/2026 12:21</t>
+          <t>4/5/2026 12:15</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>4/5/2026 12:45</t>
+          <t>4/5/2026 12:39</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="N30" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -3512,48 +3512,48 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>4/5/2026 10:42</t>
+          <t>4/5/2026 10:57</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>4/5/2026 10:59</t>
+          <t>4/5/2026 11:14</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>4/5/2026 10:59</t>
+          <t>4/5/2026 11:24</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>4/5/2026 11:01</t>
+          <t>4/5/2026 11:26</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>4/5/2026 11:01</t>
+          <t>4/5/2026 11:41</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>4/5/2026 11:13</t>
+          <t>4/5/2026 11:53</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M31" t="n">
-        <v>31</v>
+        <v>71</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="32">
@@ -3572,48 +3572,48 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>4/5/2026 11:04</t>
+          <t>4/5/2026 11:09</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>4/5/2026 11:08</t>
+          <t>4/5/2026 11:13</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>4/5/2026 11:08</t>
+          <t>4/5/2026 11:17</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>4/5/2026 11:10</t>
+          <t>4/5/2026 11:19</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>4/5/2026 11:13</t>
+          <t>4/5/2026 11:19</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>4/5/2026 11:34</t>
+          <t>4/5/2026 11:40</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="N32" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33">
@@ -3645,35 +3645,35 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>4/5/2026 11:51</t>
+          <t>4/5/2026 11:52</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>4/5/2026 11:53</t>
+          <t>4/5/2026 11:54</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>4/5/2026 11:53</t>
+          <t>4/5/2026 12:09</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>4/5/2026 11:59</t>
+          <t>4/5/2026 12:15</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M33" t="n">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="34">
@@ -4018,22 +4018,22 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>4/5/2026 09:15</t>
+          <t>4/5/2026 09:13</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>4/5/2026 09:23</t>
+          <t>4/5/2026 09:21</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -4138,22 +4138,22 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>4/5/2026 09:08</t>
+          <t>4/5/2026 09:00</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>4/5/2026 09:34</t>
+          <t>4/5/2026 09:26</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="N41" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -4172,48 +4172,48 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>4/5/2026 11:37</t>
+          <t>4/5/2026 11:42</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>4/5/2026 11:49</t>
+          <t>4/5/2026 11:54</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>4/5/2026 11:49</t>
+          <t>4/5/2026 12:04</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>4/5/2026 11:51</t>
+          <t>4/5/2026 12:06</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>4/5/2026 11:51</t>
+          <t>4/5/2026 12:21</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>4/5/2026 12:21</t>
+          <t>4/5/2026 12:51</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M42" t="n">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="43">
@@ -4305,35 +4305,35 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>4/5/2026 10:49</t>
+          <t>4/5/2026 10:57</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>4/5/2026 10:51</t>
+          <t>4/5/2026 10:59</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>4/5/2026 10:51</t>
+          <t>4/5/2026 11:07</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>4/5/2026 11:21</t>
+          <t>4/5/2026 11:37</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M44" t="n">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="45">
@@ -4472,25 +4472,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>4/5/2026 12:50</t>
+          <t>4/5/2026 13:01</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>4/5/2026 12:54</t>
+          <t>4/5/2026 13:05</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>4/5/2026 12:54</t>
+          <t>4/5/2026 13:05</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>4/5/2026 12:56</t>
+          <t>4/5/2026 13:07</t>
         </is>
       </c>
       <c r="I47" t="n">
@@ -4498,22 +4498,22 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>4/5/2026 12:56</t>
+          <t>4/5/2026 13:07</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>4/5/2026 13:23</t>
+          <t>4/5/2026 13:34</t>
         </is>
       </c>
       <c r="L47" t="n">
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="48">
@@ -4892,48 +4892,48 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>4/5/2026 11:41</t>
+          <t>4/5/2026 11:48</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>4/5/2026 11:48</t>
+          <t>4/5/2026 11:55</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>4/5/2026 11:48</t>
+          <t>4/5/2026 12:05</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>4/5/2026 11:49</t>
+          <t>4/5/2026 12:06</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>4/5/2026 11:49</t>
+          <t>4/5/2026 12:06</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>4/5/2026 11:55</t>
+          <t>4/5/2026 12:12</t>
         </is>
       </c>
       <c r="L54" t="n">
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="55">
@@ -5132,25 +5132,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>4/5/2026 10:31</t>
+          <t>4/5/2026 10:34</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>4/5/2026 10:41</t>
+          <t>4/5/2026 10:44</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>4/5/2026 10:41</t>
+          <t>4/5/2026 10:44</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>4/5/2026 10:43</t>
+          <t>4/5/2026 10:46</t>
         </is>
       </c>
       <c r="I58" t="n">
@@ -5158,22 +5158,22 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>4/5/2026 10:43</t>
+          <t>4/5/2026 11:01</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>4/5/2026 10:52</t>
+          <t>4/5/2026 11:10</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M58" t="n">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="59">
@@ -5672,48 +5672,48 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>4/5/2026 12:48</t>
+          <t>4/5/2026 13:03</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>4/5/2026 13:00</t>
+          <t>4/5/2026 13:15</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>4/5/2026 13:00</t>
+          <t>4/5/2026 13:25</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>4/5/2026 13:02</t>
+          <t>4/5/2026 13:27</t>
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>4/5/2026 13:02</t>
+          <t>4/5/2026 13:42</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>4/5/2026 13:09</t>
+          <t>4/5/2026 13:49</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M67" t="n">
-        <v>21</v>
+        <v>61</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="68">
@@ -6092,48 +6092,48 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>4/5/2026 11:04</t>
+          <t>4/5/2026 11:06</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>4/5/2026 11:08</t>
+          <t>4/5/2026 11:10</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>4/5/2026 11:08</t>
+          <t>4/5/2026 11:20</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>4/5/2026 11:10</t>
+          <t>4/5/2026 11:22</t>
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>4/5/2026 11:10</t>
+          <t>4/5/2026 11:22</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>4/5/2026 11:31</t>
+          <t>4/5/2026 11:43</t>
         </is>
       </c>
       <c r="L74" t="n">
         <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="75">
@@ -6632,48 +6632,48 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>4/5/2026 11:02</t>
+          <t>4/5/2026 11:17</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>4/5/2026 11:16</t>
+          <t>4/5/2026 11:31</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>4/5/2026 11:16</t>
+          <t>4/5/2026 11:41</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>4/5/2026 11:17</t>
+          <t>4/5/2026 11:42</t>
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>4/5/2026 11:29</t>
+          <t>4/5/2026 11:43</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>4/5/2026 11:52</t>
+          <t>4/5/2026 12:06</t>
         </is>
       </c>
       <c r="L83" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="M83" t="n">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="N83" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="84">
@@ -6692,48 +6692,48 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>4/5/2026 11:37</t>
+          <t>4/5/2026 11:41</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>4/5/2026 11:49</t>
+          <t>4/5/2026 11:53</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>4/5/2026 11:49</t>
+          <t>4/5/2026 12:02</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>4/5/2026 11:52</t>
+          <t>4/5/2026 12:05</t>
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>4/5/2026 11:52</t>
+          <t>4/5/2026 12:10</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>4/5/2026 12:22</t>
+          <t>4/5/2026 12:40</t>
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M84" t="n">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="85">
@@ -6778,22 +6778,22 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>4/5/2026 09:03</t>
+          <t>4/5/2026 09:08</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>4/5/2026 09:06</t>
+          <t>4/5/2026 09:11</t>
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M85" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="86">
@@ -6812,48 +6812,48 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>4/5/2026 08:55</t>
+          <t>4/5/2026 09:00</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>4/5/2026 09:03</t>
+          <t>4/5/2026 09:08</t>
         </is>
       </c>
       <c r="F86" t="n">
+        <v>15</v>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>4/5/2026 09:18</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>4/5/2026 09:20</t>
+        </is>
+      </c>
+      <c r="I86" t="n">
         <v>10</v>
       </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:03</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:05</t>
-        </is>
-      </c>
-      <c r="I86" t="n">
-        <v>0</v>
-      </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>4/5/2026 09:06</t>
+          <t>4/5/2026 09:21</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>4/5/2026 09:59</t>
+          <t>4/5/2026 10:14</t>
         </is>
       </c>
       <c r="L86" t="n">
         <v>1</v>
       </c>
       <c r="M86" t="n">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="N86" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
     </row>
     <row r="87">
@@ -7352,48 +7352,48 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>4/5/2026 11:04</t>
+          <t>4/5/2026 11:08</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>4/5/2026 11:09</t>
+          <t>4/5/2026 11:13</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>4/5/2026 11:09</t>
+          <t>4/5/2026 11:23</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>4/5/2026 11:11</t>
+          <t>4/5/2026 11:25</t>
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>4/5/2026 11:11</t>
+          <t>4/5/2026 11:25</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>4/5/2026 11:32</t>
+          <t>4/5/2026 11:46</t>
         </is>
       </c>
       <c r="L95" t="n">
         <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="96">
@@ -7472,25 +7472,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>4/5/2026 11:13</t>
+          <t>4/5/2026 11:14</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>4/5/2026 11:25</t>
+          <t>4/5/2026 11:26</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>4/5/2026 11:25</t>
+          <t>4/5/2026 11:26</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>4/5/2026 11:28</t>
+          <t>4/5/2026 11:29</t>
         </is>
       </c>
       <c r="I97" t="n">
@@ -7498,22 +7498,22 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>4/5/2026 11:28</t>
+          <t>4/5/2026 11:29</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>4/5/2026 11:48</t>
+          <t>4/5/2026 11:49</t>
         </is>
       </c>
       <c r="L97" t="n">
         <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98">
@@ -7652,25 +7652,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>4/5/2026 10:31</t>
+          <t>4/5/2026 10:46</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>4/5/2026 10:44</t>
+          <t>4/5/2026 10:59</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>4/5/2026 10:44</t>
+          <t>4/5/2026 10:59</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>4/5/2026 10:46</t>
+          <t>4/5/2026 11:01</t>
         </is>
       </c>
       <c r="I100" t="n">
@@ -7678,22 +7678,22 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>4/5/2026 10:46</t>
+          <t>4/5/2026 11:02</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>4/5/2026 10:55</t>
+          <t>4/5/2026 11:11</t>
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M100" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="101">
@@ -7772,48 +7772,48 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>4/5/2026 09:07</t>
+          <t>4/5/2026 09:04</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>4/5/2026 09:14</t>
+          <t>4/5/2026 09:11</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>4/5/2026 09:15</t>
+          <t>4/5/2026 09:11</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>4/5/2026 09:17</t>
+          <t>4/5/2026 09:13</t>
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>4/5/2026 09:17</t>
+          <t>4/5/2026 09:13</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>4/5/2026 09:25</t>
+          <t>4/5/2026 09:21</t>
         </is>
       </c>
       <c r="L102" t="n">
         <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="N102" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -7952,48 +7952,48 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>4/5/2026 08:40</t>
+          <t>4/5/2026 08:36</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>4/5/2026 08:55</t>
+          <t>4/5/2026 08:51</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>4/5/2026 09:05</t>
+          <t>4/5/2026 08:51</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>4/5/2026 09:07</t>
+          <t>4/5/2026 08:53</t>
         </is>
       </c>
       <c r="I105" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>4/5/2026 09:27</t>
+          <t>4/5/2026 09:02</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>4/5/2026 10:00</t>
+          <t>4/5/2026 09:35</t>
         </is>
       </c>
       <c r="L105" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="M105" t="n">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="N105" t="n">
-        <v>38</v>
+        <v>13</v>
       </c>
     </row>
     <row r="106">
@@ -8038,22 +8038,22 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>4/5/2026 09:03</t>
+          <t>4/5/2026 09:08</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>4/5/2026 09:06</t>
+          <t>4/5/2026 09:11</t>
         </is>
       </c>
       <c r="L106" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M106" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/Thesis_TSSP_NEW_M1_Results_5_Scenarios.xlsx
+++ b/Thesis_TSSP_NEW_M1_Results_5_Scenarios.xlsx
@@ -468,7 +468,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>4/5/2026 15:45</t>
+          <t>4/5/2026 15:32</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -478,7 +478,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>4/5/2026 15:45</t>
+          <t>4/5/2026 08:45</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -488,7 +488,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>4/5/2026 15:45</t>
+          <t>4/5/2026 10:48</t>
         </is>
       </c>
     </row>
@@ -505,7 +505,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>4/5/2026 15:45</t>
+          <t>4/5/2026 15:32</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -515,7 +515,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>4/5/2026 15:45</t>
+          <t>4/5/2026 09:13</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>4/5/2026 15:45</t>
+          <t>4/5/2026 12:11</t>
         </is>
       </c>
     </row>
@@ -537,32 +537,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Unload Gate 4</t>
+          <t>Unload Gate 2</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4/5/2026 15:45</t>
+          <t>4/5/2026 15:32</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Transport Cart 1</t>
+          <t>Transport Cart 3</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>4/5/2026 15:45</t>
+          <t>4/5/2026 11:41</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Infeed Station 3</t>
+          <t>Infeed Station 2</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>4/5/2026 15:45</t>
+          <t>4/5/2026 13:00</t>
         </is>
       </c>
     </row>
@@ -574,12 +574,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Unload Gate 3</t>
+          <t>Unload Gate 4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>4/5/2026 15:45</t>
+          <t>4/5/2026 08:57</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -589,17 +589,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>4/5/2026 09:01</t>
+          <t>4/5/2026 15:32</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Infeed Station 2</t>
+          <t>Infeed Station 3</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>4/5/2026 15:45</t>
+          <t>4/5/2026 10:23</t>
         </is>
       </c>
     </row>
@@ -616,27 +616,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4/5/2026 15:45</t>
+          <t>4/5/2026 10:56</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Transport Cart 1</t>
+          <t>Transport Cart 2</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>4/5/2026 15:45</t>
+          <t>4/5/2026 09:08</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Infeed Station 1</t>
+          <t>Infeed Station 3</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>4/5/2026 15:45</t>
+          <t>4/5/2026 09:12</t>
         </is>
       </c>
     </row>
@@ -648,12 +648,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Unload Gate 2</t>
+          <t>Unload Gate 1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>4/5/2026 07:19</t>
+          <t>4/5/2026 10:34</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -663,7 +663,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>4/5/2026 07:44</t>
+          <t>4/5/2026 10:23</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -673,7 +673,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>4/5/2026 08:04</t>
+          <t>4/5/2026 07:30</t>
         </is>
       </c>
     </row>
@@ -690,27 +690,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>4/5/2026 15:14</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Transport Cart 2</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>4/5/2026 06:48</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Transport Cart 2</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>4/5/2026 07:16</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Infeed Station 1</t>
+          <t>Infeed Station 2</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>4/5/2026 07:00</t>
+          <t>4/5/2026 07:07</t>
         </is>
       </c>
     </row>
@@ -722,12 +722,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Unload Gate 2</t>
+          <t>Unload Gate 3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>4/5/2026 10:38</t>
+          <t>4/5/2026 15:32</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -737,17 +737,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>4/5/2026 12:00</t>
+          <t>4/5/2026 09:21</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Infeed Station 1</t>
+          <t>Infeed Station 2</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>4/5/2026 11:17</t>
+          <t>4/5/2026 11:04</t>
         </is>
       </c>
     </row>
@@ -759,12 +759,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Unload Gate 2</t>
+          <t>Unload Gate 3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>4/5/2026 10:31</t>
+          <t>4/5/2026 10:32</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -774,17 +774,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>4/5/2026 08:28</t>
+          <t>4/5/2026 09:39</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Infeed Station 1</t>
+          <t>Infeed Station 2</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>4/5/2026 09:44</t>
+          <t>4/5/2026 08:47</t>
         </is>
       </c>
     </row>
@@ -796,32 +796,32 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Unload Gate 3</t>
+          <t>Unload Gate 1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>4/5/2026 10:02</t>
+          <t>4/5/2026 14:28</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Transport Cart 3</t>
+          <t>Transport Cart 2</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>4/5/2026 12:39</t>
+          <t>4/5/2026 07:27</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Infeed Station 2</t>
+          <t>Infeed Station 3</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>4/5/2026 15:45</t>
+          <t>4/5/2026 11:10</t>
         </is>
       </c>
     </row>
@@ -833,7 +833,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Unload Gate 4</t>
+          <t>Unload Gate 3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -843,22 +843,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Transport Cart 2</t>
+          <t>Transport Cart 1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>4/5/2026 08:06</t>
+          <t>4/5/2026 10:57</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Infeed Station 1</t>
+          <t>Infeed Station 3</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>4/5/2026 15:41</t>
+          <t>4/5/2026 11:50</t>
         </is>
       </c>
     </row>
@@ -870,22 +870,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Unload Gate 4</t>
+          <t>Unload Gate 2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>4/5/2026 10:12</t>
+          <t>4/5/2026 15:29</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Transport Cart 2</t>
+          <t>Transport Cart 1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>4/5/2026 08:32</t>
+          <t>4/5/2026 14:05</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>4/5/2026 09:23</t>
+          <t>4/5/2026 11:27</t>
         </is>
       </c>
     </row>
@@ -912,27 +912,27 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>4/5/2026 08:47</t>
+          <t>4/5/2026 08:40</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Transport Cart 3</t>
+          <t>Transport Cart 2</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>4/5/2026 14:28</t>
+          <t>4/5/2026 08:40</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Infeed Station 3</t>
+          <t>Infeed Station 1</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>4/5/2026 12:36</t>
+          <t>4/5/2026 09:14</t>
         </is>
       </c>
     </row>
@@ -949,7 +949,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>4/5/2026 15:41</t>
+          <t>4/5/2026 15:21</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -959,17 +959,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>4/5/2026 07:25</t>
+          <t>4/5/2026 06:18</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Infeed Station 3</t>
+          <t>Infeed Station 2</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>4/5/2026 08:03</t>
+          <t>4/5/2026 06:21</t>
         </is>
       </c>
     </row>
@@ -981,32 +981,32 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Unload Gate 3</t>
+          <t>Unload Gate 4</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>4/5/2026 15:37</t>
+          <t>4/5/2026 10:47</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Transport Cart 3</t>
+          <t>Transport Cart 1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>4/5/2026 08:23</t>
+          <t>4/5/2026 07:41</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Infeed Station 2</t>
+          <t>Infeed Station 3</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>4/5/2026 13:46</t>
+          <t>4/5/2026 08:39</t>
         </is>
       </c>
     </row>
@@ -1018,12 +1018,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Unload Gate 4</t>
+          <t>Unload Gate 1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>4/5/2026 12:34</t>
+          <t>4/5/2026 09:15</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>4/5/2026 14:58</t>
+          <t>4/5/2026 09:14</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>4/5/2026 15:42</t>
+          <t>4/5/2026 09:40</t>
         </is>
       </c>
     </row>
@@ -1055,32 +1055,32 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Unload Gate 3</t>
+          <t>Unload Gate 1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>4/5/2026 09:46</t>
+          <t>4/5/2026 12:24</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Transport Cart 2</t>
+          <t>Transport Cart 1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>4/5/2026 15:29</t>
+          <t>4/5/2026 15:16</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Infeed Station 1</t>
+          <t>Infeed Station 3</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>4/5/2026 09:35</t>
+          <t>4/5/2026 09:23</t>
         </is>
       </c>
     </row>
@@ -1092,32 +1092,32 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Unload Gate 1</t>
+          <t>Unload Gate 4</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>4/5/2026 13:59</t>
+          <t>4/5/2026 09:46</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Transport Cart 2</t>
+          <t>Transport Cart 1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>4/5/2026 15:43</t>
+          <t>4/5/2026 14:32</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Infeed Station 2</t>
+          <t>Infeed Station 3</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>4/5/2026 09:17</t>
+          <t>4/5/2026 09:49</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>4/5/2026 12:21</t>
+          <t>4/5/2026 12:54</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Transport Cart 3</t>
+          <t>Transport Cart 2</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>4/5/2026 08:46</t>
+          <t>4/5/2026 09:12</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>4/5/2026 09:10</t>
+          <t>4/5/2026 10:37</t>
         </is>
       </c>
     </row>
@@ -1166,12 +1166,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Unload Gate 1</t>
+          <t>Unload Gate 4</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>4/5/2026 09:01</t>
+          <t>4/5/2026 10:10</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>4/5/2026 15:14</t>
+          <t>4/5/2026 11:54</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>4/5/2026 12:40</t>
+          <t>4/5/2026 11:41</t>
         </is>
       </c>
     </row>
@@ -1203,32 +1203,32 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Unload Gate 3</t>
+          <t>Unload Gate 2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>4/5/2026 13:45</t>
+          <t>4/5/2026 13:37</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Transport Cart 2</t>
+          <t>Transport Cart 3</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>4/5/2026 08:56</t>
+          <t>4/5/2026 15:32</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Infeed Station 1</t>
+          <t>Infeed Station 3</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>4/5/2026 09:01</t>
+          <t>4/5/2026 09:05</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>436.20 min</t>
+          <t>422.20 min</t>
         </is>
       </c>
     </row>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>34.88 min</t>
+          <t>39.65 min</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>86.60 min</t>
+          <t>92.40 min</t>
         </is>
       </c>
     </row>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>93.00 min</t>
+          <t>120.00 min</t>
         </is>
       </c>
     </row>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>29.60 min</t>
+          <t>27.00 min</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>14.20/10.00/12.60 min</t>
+          <t>10.00/7.00/10.00 min</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>567873 / 31736</t>
+          <t>551598 / 31296</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>21.2800 sec</t>
+          <t>29.2020 sec</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1.4136 %</t>
+          <t>1.2211 %</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21">
@@ -1457,7 +1457,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>35.90 min | 93.00 min</t>
+          <t>43.14 min | 120.00 min</t>
         </is>
       </c>
     </row>
@@ -1514,7 +1514,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>34.95 min | 86.00 min</t>
+          <t>36.90 min | 86.00 min</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>33.38 min | 83.00 min</t>
+          <t>36.52 min | 83.00 min</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>36.57 min | 82.00 min</t>
+          <t>40.57 min | 83.00 min</t>
         </is>
       </c>
     </row>
@@ -1550,7 +1550,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>33.57 min | 89.00 min</t>
+          <t>41.10 min | 90.00 min</t>
         </is>
       </c>
     </row>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>6.75</v>
+        <v>11.63</v>
       </c>
     </row>
     <row r="36">
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>15.76</v>
+        <v>16.28</v>
       </c>
     </row>
     <row r="37">
@@ -1597,7 +1597,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>13.51</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="38">
@@ -1607,7 +1607,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>11.26</v>
+        <v>11.63</v>
       </c>
     </row>
     <row r="39">
@@ -1617,7 +1617,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2.19</v>
+        <v>3.63</v>
       </c>
     </row>
     <row r="40">
@@ -1627,7 +1627,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4.83</v>
+        <v>4.53</v>
       </c>
     </row>
     <row r="41">
@@ -1637,7 +1637,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>2.19</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="42">
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>43.6</v>
+        <v>18.02</v>
       </c>
     </row>
     <row r="43">
@@ -1657,7 +1657,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>26.16</v>
+        <v>31.53</v>
       </c>
     </row>
     <row r="44">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>21.8</v>
+        <v>45.05</v>
       </c>
     </row>
   </sheetData>
@@ -1772,48 +1772,48 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>4/5/2026 08:51</t>
+          <t>4/5/2026 08:55</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>4/5/2026 09:02</t>
+          <t>4/5/2026 09:06</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>4/5/2026 09:12</t>
+          <t>4/5/2026 09:13</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>4/5/2026 09:14</t>
+          <t>4/5/2026 09:15</t>
         </is>
       </c>
       <c r="I2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>4/5/2026 09:25</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>4/5/2026 10:18</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
         <v>10</v>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:22</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>4/5/2026 10:15</t>
-        </is>
-      </c>
-      <c r="L2" t="n">
-        <v>8</v>
-      </c>
       <c r="M2" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="N2" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3">
@@ -1832,48 +1832,48 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>4/5/2026 09:13</t>
+          <t>4/5/2026 09:23</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>4/5/2026 09:40</t>
+          <t>4/5/2026 09:50</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>4/5/2026 09:40</t>
+          <t>4/5/2026 09:57</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>4/5/2026 09:42</t>
+          <t>4/5/2026 09:59</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>4/5/2026 09:42</t>
+          <t>4/5/2026 10:09</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>4/5/2026 10:46</t>
+          <t>4/5/2026 11:13</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M3" t="n">
-        <v>93</v>
+        <v>120</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4">
@@ -1892,25 +1892,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4/5/2026 12:53</t>
+          <t>4/5/2026 12:48</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>4/5/2026 13:05</t>
+          <t>4/5/2026 13:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>4/5/2026 13:05</t>
+          <t>4/5/2026 13:00</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>4/5/2026 13:07</t>
+          <t>4/5/2026 13:02</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -1918,22 +1918,22 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>4/5/2026 13:07</t>
+          <t>4/5/2026 13:02</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>4/5/2026 13:14</t>
+          <t>4/5/2026 13:09</t>
         </is>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -2038,22 +2038,22 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
+          <t>4/5/2026 09:12</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
           <t>4/5/2026 09:13</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:14</t>
-        </is>
-      </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -2098,22 +2098,22 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>4/5/2026 07:29</t>
+          <t>4/5/2026 07:30</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>4/5/2026 07:45</t>
+          <t>4/5/2026 07:46</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -2132,25 +2132,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>4/5/2026 06:48</t>
+          <t>4/5/2026 06:50</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>4/5/2026 07:03</t>
+          <t>4/5/2026 07:05</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>4/5/2026 07:03</t>
+          <t>4/5/2026 07:05</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4/5/2026 07:05</t>
+          <t>4/5/2026 07:07</t>
         </is>
       </c>
       <c r="I8" t="n">
@@ -2158,22 +2158,22 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>4/5/2026 07:05</t>
+          <t>4/5/2026 07:07</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>4/5/2026 07:28</t>
+          <t>4/5/2026 07:30</t>
         </is>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -2192,48 +2192,48 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>4/5/2026 10:26</t>
+          <t>4/5/2026 10:36</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>4/5/2026 10:35</t>
+          <t>4/5/2026 10:45</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>4/5/2026 10:35</t>
+          <t>4/5/2026 10:52</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>4/5/2026 10:37</t>
+          <t>4/5/2026 10:54</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>4/5/2026 10:37</t>
+          <t>4/5/2026 11:04</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>4/5/2026 11:06</t>
+          <t>4/5/2026 11:33</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M9" t="n">
-        <v>40</v>
+        <v>67</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10">
@@ -2278,22 +2278,22 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4/5/2026 08:40</t>
+          <t>4/5/2026 08:47</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>4/5/2026 09:10</t>
+          <t>4/5/2026 09:17</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M10" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
@@ -2312,48 +2312,48 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>4/5/2026 07:25</t>
+          <t>4/5/2026 07:35</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>4/5/2026 07:29</t>
+          <t>4/5/2026 07:39</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>4/5/2026 07:29</t>
+          <t>4/5/2026 07:46</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>4/5/2026 07:31</t>
+          <t>4/5/2026 07:48</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>4/5/2026 07:31</t>
+          <t>4/5/2026 07:58</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>4/5/2026 07:46</t>
+          <t>4/5/2026 08:13</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M11" t="n">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12">
@@ -2372,25 +2372,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>4/5/2026 11:56</t>
+          <t>4/5/2026 11:41</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>4/5/2026 12:06</t>
+          <t>4/5/2026 11:51</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>4/5/2026 12:06</t>
+          <t>4/5/2026 11:51</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>4/5/2026 12:07</t>
+          <t>4/5/2026 11:52</t>
         </is>
       </c>
       <c r="I12" t="n">
@@ -2398,22 +2398,22 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>4/5/2026 12:16</t>
+          <t>4/5/2026 11:52</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>4/5/2026 12:22</t>
+          <t>4/5/2026 11:58</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="N12" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -2518,22 +2518,22 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>4/5/2026 08:49</t>
+          <t>4/5/2026 08:57</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>4/5/2026 09:17</t>
+          <t>4/5/2026 09:25</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M14" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
@@ -2578,22 +2578,22 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>4/5/2026 06:20</t>
+          <t>4/5/2026 06:21</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>4/5/2026 06:22</t>
+          <t>4/5/2026 06:23</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -2638,22 +2638,22 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>4/5/2026 08:42</t>
+          <t>4/5/2026 08:39</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>4/5/2026 08:50</t>
+          <t>4/5/2026 08:47</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="N16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2672,48 +2672,48 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>4/5/2026 09:09</t>
+          <t>4/5/2026 09:19</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>4/5/2026 09:22</t>
+          <t>4/5/2026 09:32</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>4/5/2026 09:22</t>
+          <t>4/5/2026 09:35</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>4/5/2026 09:23</t>
+          <t>4/5/2026 09:36</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>4/5/2026 09:23</t>
+          <t>4/5/2026 09:40</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>4/5/2026 09:32</t>
+          <t>4/5/2026 09:49</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M17" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18">
@@ -2732,48 +2732,48 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>4/5/2026 09:04</t>
+          <t>4/5/2026 09:06</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>4/5/2026 09:09</t>
+          <t>4/5/2026 09:11</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>4/5/2026 09:09</t>
+          <t>4/5/2026 09:15</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>4/5/2026 09:12</t>
+          <t>4/5/2026 09:18</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>4/5/2026 09:14</t>
+          <t>4/5/2026 09:23</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>4/5/2026 09:22</t>
+          <t>4/5/2026 09:31</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M18" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="N18" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19">
@@ -2792,48 +2792,48 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>4/5/2026 09:16</t>
+          <t>4/5/2026 09:18</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>4/5/2026 09:35</t>
+          <t>4/5/2026 09:37</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>4/5/2026 09:35</t>
+          <t>4/5/2026 09:44</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>4/5/2026 09:37</t>
+          <t>4/5/2026 09:46</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>4/5/2026 09:37</t>
+          <t>4/5/2026 09:49</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>4/5/2026 09:57</t>
+          <t>4/5/2026 10:09</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M19" t="n">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20">
@@ -2852,48 +2852,48 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>4/5/2026 09:58</t>
+          <t>4/5/2026 10:08</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>4/5/2026 10:13</t>
+          <t>4/5/2026 10:23</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>4/5/2026 10:13</t>
+          <t>4/5/2026 10:29</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>4/5/2026 10:15</t>
+          <t>4/5/2026 10:31</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>4/5/2026 10:15</t>
+          <t>4/5/2026 10:37</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>4/5/2026 10:42</t>
+          <t>4/5/2026 11:04</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M20" t="n">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -2912,48 +2912,48 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>4/5/2026 08:32</t>
+          <t>4/5/2026 08:42</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>4/5/2026 08:46</t>
+          <t>4/5/2026 08:56</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>4/5/2026 08:46</t>
+          <t>4/5/2026 09:03</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>4/5/2026 08:50</t>
+          <t>4/5/2026 09:07</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>4/5/2026 08:50</t>
+          <t>4/5/2026 09:17</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>4/5/2026 09:23</t>
+          <t>4/5/2026 09:50</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M21" t="n">
-        <v>51</v>
+        <v>78</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="22">
@@ -2998,22 +2998,22 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>4/5/2026 09:10</t>
+          <t>4/5/2026 09:05</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>4/5/2026 09:13</t>
+          <t>4/5/2026 09:08</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="N22" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -3152,48 +3152,48 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>4/5/2026 13:03</t>
+          <t>4/5/2026 12:48</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>4/5/2026 13:12</t>
+          <t>4/5/2026 12:57</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>4/5/2026 13:21</t>
+          <t>4/5/2026 12:57</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>4/5/2026 13:24</t>
+          <t>4/5/2026 13:00</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>4/5/2026 13:24</t>
+          <t>4/5/2026 13:00</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>4/5/2026 13:31</t>
+          <t>4/5/2026 13:07</t>
         </is>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="N25" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -3212,48 +3212,48 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t>4/5/2026 10:03</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>4/5/2026 10:05</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>4/5/2026 10:07</t>
-        </is>
-      </c>
       <c r="F26" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>4/5/2026 10:07</t>
+          <t>4/5/2026 10:12</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>4/5/2026 10:09</t>
+          <t>4/5/2026 10:14</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>4/5/2026 10:09</t>
+          <t>4/5/2026 10:23</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>4/5/2026 10:16</t>
+          <t>4/5/2026 10:30</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M26" t="n">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="N26" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="27">
@@ -3358,22 +3358,22 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>4/5/2026 07:29</t>
+          <t>4/5/2026 07:30</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>4/5/2026 07:45</t>
+          <t>4/5/2026 07:46</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M28" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -3418,22 +3418,22 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>4/5/2026 07:05</t>
+          <t>4/5/2026 07:07</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>4/5/2026 07:28</t>
+          <t>4/5/2026 07:30</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M29" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -3478,22 +3478,22 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>4/5/2026 12:15</t>
+          <t>4/5/2026 12:21</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>4/5/2026 12:39</t>
+          <t>4/5/2026 12:45</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M30" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31">
@@ -3512,48 +3512,48 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>4/5/2026 10:57</t>
+          <t>4/5/2026 10:42</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>4/5/2026 11:14</t>
+          <t>4/5/2026 10:59</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>4/5/2026 11:24</t>
+          <t>4/5/2026 10:59</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>4/5/2026 11:26</t>
+          <t>4/5/2026 11:01</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>4/5/2026 11:41</t>
+          <t>4/5/2026 11:01</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>4/5/2026 11:53</t>
+          <t>4/5/2026 11:13</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>71</v>
+        <v>31</v>
       </c>
       <c r="N31" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -3572,48 +3572,48 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>4/5/2026 11:09</t>
+          <t>4/5/2026 11:04</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>4/5/2026 11:13</t>
+          <t>4/5/2026 11:08</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>4/5/2026 11:17</t>
+          <t>4/5/2026 11:08</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>4/5/2026 11:19</t>
+          <t>4/5/2026 11:10</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>4/5/2026 11:19</t>
+          <t>4/5/2026 11:10</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>4/5/2026 11:40</t>
+          <t>4/5/2026 11:31</t>
         </is>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="N32" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -3645,35 +3645,35 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>4/5/2026 11:52</t>
+          <t>4/5/2026 11:51</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>4/5/2026 11:54</t>
+          <t>4/5/2026 11:53</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>4/5/2026 12:09</t>
+          <t>4/5/2026 11:53</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>4/5/2026 12:15</t>
+          <t>4/5/2026 11:59</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="N33" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -3705,35 +3705,35 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>4/5/2026 08:34</t>
+          <t>4/5/2026 08:36</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>4/5/2026 08:35</t>
+          <t>4/5/2026 08:37</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>4/5/2026 08:35</t>
+          <t>4/5/2026 08:47</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>4/5/2026 09:02</t>
+          <t>4/5/2026 09:14</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M34" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="35">
@@ -3752,48 +3752,48 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>4/5/2026 08:40</t>
+          <t>4/5/2026 08:50</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>4/5/2026 08:45</t>
+          <t>4/5/2026 08:55</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>4/5/2026 08:45</t>
+          <t>4/5/2026 09:02</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>4/5/2026 08:47</t>
+          <t>4/5/2026 09:04</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>4/5/2026 08:47</t>
+          <t>4/5/2026 09:14</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>4/5/2026 09:15</t>
+          <t>4/5/2026 09:42</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M35" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="36">
@@ -3872,48 +3872,48 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>4/5/2026 07:08</t>
+          <t>4/5/2026 07:18</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>4/5/2026 07:20</t>
+          <t>4/5/2026 07:30</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>4/5/2026 07:20</t>
+          <t>4/5/2026 07:37</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>4/5/2026 07:22</t>
+          <t>4/5/2026 07:39</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>4/5/2026 07:22</t>
+          <t>4/5/2026 07:49</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>4/5/2026 07:29</t>
+          <t>4/5/2026 07:56</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M37" t="n">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="38">
@@ -3932,25 +3932,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>4/5/2026 09:09</t>
+          <t>4/5/2026 09:19</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>4/5/2026 09:19</t>
+          <t>4/5/2026 09:29</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>4/5/2026 09:19</t>
+          <t>4/5/2026 09:29</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>4/5/2026 09:21</t>
+          <t>4/5/2026 09:31</t>
         </is>
       </c>
       <c r="I38" t="n">
@@ -3958,22 +3958,22 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>4/5/2026 09:21</t>
+          <t>4/5/2026 09:40</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>4/5/2026 09:30</t>
+          <t>4/5/2026 09:49</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M38" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="39">
@@ -4018,22 +4018,22 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>4/5/2026 09:13</t>
+          <t>4/5/2026 09:23</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>4/5/2026 09:21</t>
+          <t>4/5/2026 09:31</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M39" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="40">
@@ -4052,25 +4052,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>4/5/2026 09:16</t>
+          <t>4/5/2026 09:26</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>4/5/2026 09:32</t>
+          <t>4/5/2026 09:42</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>4/5/2026 09:32</t>
+          <t>4/5/2026 09:42</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>4/5/2026 09:34</t>
+          <t>4/5/2026 09:44</t>
         </is>
       </c>
       <c r="I40" t="n">
@@ -4078,22 +4078,22 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>4/5/2026 09:34</t>
+          <t>4/5/2026 09:49</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>4/5/2026 09:54</t>
+          <t>4/5/2026 10:09</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M40" t="n">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="41">
@@ -4112,48 +4112,48 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>4/5/2026 08:45</t>
+          <t>4/5/2026 08:55</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>4/5/2026 08:59</t>
+          <t>4/5/2026 09:09</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>4/5/2026 08:59</t>
+          <t>4/5/2026 09:16</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>4/5/2026 09:00</t>
+          <t>4/5/2026 09:17</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>4/5/2026 09:00</t>
+          <t>4/5/2026 09:27</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>4/5/2026 09:26</t>
+          <t>4/5/2026 09:53</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M41" t="n">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="42">
@@ -4172,48 +4172,48 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>4/5/2026 11:42</t>
+          <t>4/5/2026 11:37</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>4/5/2026 11:54</t>
+          <t>4/5/2026 11:49</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>4/5/2026 12:04</t>
+          <t>4/5/2026 11:49</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>4/5/2026 12:06</t>
+          <t>4/5/2026 11:51</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
+          <t>4/5/2026 11:51</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
           <t>4/5/2026 12:21</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>4/5/2026 12:51</t>
-        </is>
-      </c>
       <c r="L42" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="N42" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -4305,35 +4305,35 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>4/5/2026 10:57</t>
+          <t>4/5/2026 10:49</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>4/5/2026 10:59</t>
+          <t>4/5/2026 10:51</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>4/5/2026 11:07</t>
+          <t>4/5/2026 10:51</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>4/5/2026 11:37</t>
+          <t>4/5/2026 11:21</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="N44" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -4412,48 +4412,48 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>4/5/2026 06:00</t>
+          <t>4/5/2026 06:10</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>4/5/2026 06:02</t>
+          <t>4/5/2026 06:12</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>4/5/2026 06:02</t>
+          <t>4/5/2026 06:19</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>4/5/2026 06:04</t>
+          <t>4/5/2026 06:21</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>4/5/2026 06:04</t>
+          <t>4/5/2026 06:31</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>4/5/2026 06:06</t>
+          <t>4/5/2026 06:33</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M46" t="n">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="47">
@@ -4472,25 +4472,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>4/5/2026 13:01</t>
+          <t>4/5/2026 12:50</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>4/5/2026 13:05</t>
+          <t>4/5/2026 12:54</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>4/5/2026 13:05</t>
+          <t>4/5/2026 12:54</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>4/5/2026 13:07</t>
+          <t>4/5/2026 12:56</t>
         </is>
       </c>
       <c r="I47" t="n">
@@ -4498,22 +4498,22 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>4/5/2026 13:07</t>
+          <t>4/5/2026 12:57</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>4/5/2026 13:34</t>
+          <t>4/5/2026 13:24</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M47" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="N47" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -4712,48 +4712,48 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>4/5/2026 10:26</t>
+          <t>4/5/2026 10:36</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>4/5/2026 10:36</t>
+          <t>4/5/2026 10:46</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>4/5/2026 10:36</t>
+          <t>4/5/2026 10:53</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>4/5/2026 10:38</t>
+          <t>4/5/2026 10:55</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>4/5/2026 10:38</t>
+          <t>4/5/2026 11:04</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>4/5/2026 11:07</t>
+          <t>4/5/2026 11:33</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M51" t="n">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
     </row>
     <row r="52">
@@ -4892,48 +4892,48 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
+          <t>4/5/2026 11:41</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
           <t>4/5/2026 11:48</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>4/5/2026 11:55</t>
-        </is>
-      </c>
       <c r="F54" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>4/5/2026 12:05</t>
+          <t>4/5/2026 11:48</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>4/5/2026 12:06</t>
+          <t>4/5/2026 11:49</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>4/5/2026 12:06</t>
+          <t>4/5/2026 11:50</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>4/5/2026 12:12</t>
+          <t>4/5/2026 11:56</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M54" t="n">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="N54" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -4952,48 +4952,48 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>4/5/2026 08:24</t>
+          <t>4/5/2026 08:34</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>4/5/2026 08:32</t>
+          <t>4/5/2026 08:42</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>4/5/2026 08:32</t>
+          <t>4/5/2026 08:49</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>4/5/2026 08:33</t>
+          <t>4/5/2026 08:50</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>4/5/2026 08:33</t>
+          <t>4/5/2026 09:00</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>4/5/2026 09:00</t>
+          <t>4/5/2026 09:27</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M55" t="n">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="56">
@@ -5038,22 +5038,22 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>4/5/2026 11:17</t>
+          <t>4/5/2026 11:21</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>4/5/2026 11:54</t>
+          <t>4/5/2026 11:58</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M56" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="57">
@@ -5098,22 +5098,22 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>4/5/2026 06:20</t>
+          <t>4/5/2026 06:21</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>4/5/2026 06:22</t>
+          <t>4/5/2026 06:23</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M57" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -5132,25 +5132,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>4/5/2026 10:34</t>
+          <t>4/5/2026 10:31</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>4/5/2026 10:44</t>
+          <t>4/5/2026 10:41</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>4/5/2026 10:44</t>
+          <t>4/5/2026 10:41</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>4/5/2026 10:46</t>
+          <t>4/5/2026 10:43</t>
         </is>
       </c>
       <c r="I58" t="n">
@@ -5158,22 +5158,22 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>4/5/2026 11:01</t>
+          <t>4/5/2026 10:43</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>4/5/2026 11:10</t>
+          <t>4/5/2026 10:52</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="N58" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -5192,48 +5192,48 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>4/5/2026 09:09</t>
+          <t>4/5/2026 09:18</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>4/5/2026 09:19</t>
+          <t>4/5/2026 09:28</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>4/5/2026 09:19</t>
+          <t>4/5/2026 09:34</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>4/5/2026 09:21</t>
+          <t>4/5/2026 09:36</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>4/5/2026 09:21</t>
+          <t>4/5/2026 09:40</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>4/5/2026 09:30</t>
+          <t>4/5/2026 09:49</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M59" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="60">
@@ -5278,22 +5278,22 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>4/5/2026 09:13</t>
+          <t>4/5/2026 09:23</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>4/5/2026 09:21</t>
+          <t>4/5/2026 09:31</t>
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M60" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="61">
@@ -5325,35 +5325,35 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>4/5/2026 09:34</t>
+          <t>4/5/2026 09:39</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>4/5/2026 09:37</t>
+          <t>4/5/2026 09:42</t>
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>4/5/2026 09:37</t>
+          <t>4/5/2026 09:49</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>4/5/2026 09:57</t>
+          <t>4/5/2026 10:09</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M61" t="n">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="62">
@@ -5638,22 +5638,22 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>4/5/2026 12:10</t>
+          <t>4/5/2026 12:11</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>4/5/2026 12:56</t>
+          <t>4/5/2026 12:57</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M66" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -5672,48 +5672,48 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>4/5/2026 13:03</t>
+          <t>4/5/2026 12:48</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>4/5/2026 13:15</t>
+          <t>4/5/2026 13:00</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>4/5/2026 13:25</t>
+          <t>4/5/2026 13:00</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>4/5/2026 13:27</t>
+          <t>4/5/2026 13:02</t>
         </is>
       </c>
       <c r="I67" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>4/5/2026 13:42</t>
+          <t>4/5/2026 13:02</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>4/5/2026 13:49</t>
+          <t>4/5/2026 13:09</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>61</v>
+        <v>21</v>
       </c>
       <c r="N67" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -5732,48 +5732,48 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>4/5/2026 09:53</t>
+          <t>4/5/2026 10:03</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>4/5/2026 09:55</t>
+          <t>4/5/2026 10:05</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>4/5/2026 09:55</t>
+          <t>4/5/2026 10:12</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>4/5/2026 09:56</t>
+          <t>4/5/2026 10:13</t>
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>4/5/2026 09:56</t>
+          <t>4/5/2026 10:23</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>4/5/2026 10:03</t>
+          <t>4/5/2026 10:30</t>
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M68" t="n">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="69">
@@ -5818,22 +5818,22 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>4/5/2026 09:11</t>
+          <t>4/5/2026 09:12</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>4/5/2026 09:12</t>
+          <t>4/5/2026 09:13</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M69" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -5878,22 +5878,22 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>4/5/2026 07:29</t>
+          <t>4/5/2026 07:30</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>4/5/2026 07:45</t>
+          <t>4/5/2026 07:46</t>
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M70" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -5912,25 +5912,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>4/5/2026 06:48</t>
+          <t>4/5/2026 06:54</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>4/5/2026 06:59</t>
+          <t>4/5/2026 07:05</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>4/5/2026 06:59</t>
+          <t>4/5/2026 07:05</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>4/5/2026 07:01</t>
+          <t>4/5/2026 07:07</t>
         </is>
       </c>
       <c r="I71" t="n">
@@ -5938,22 +5938,22 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>4/5/2026 07:01</t>
+          <t>4/5/2026 07:07</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>4/5/2026 07:24</t>
+          <t>4/5/2026 07:30</t>
         </is>
       </c>
       <c r="L71" t="n">
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="72">
@@ -5972,48 +5972,48 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>4/5/2026 09:20</t>
+          <t>4/5/2026 09:30</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>4/5/2026 09:29</t>
+          <t>4/5/2026 09:39</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>4/5/2026 09:29</t>
+          <t>4/5/2026 09:46</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>4/5/2026 09:30</t>
+          <t>4/5/2026 09:47</t>
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>4/5/2026 09:30</t>
+          <t>4/5/2026 09:57</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>4/5/2026 10:11</t>
+          <t>4/5/2026 10:38</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M72" t="n">
-        <v>51</v>
+        <v>78</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="73">
@@ -6045,35 +6045,35 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>4/5/2026 08:35</t>
+          <t>4/5/2026 08:42</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>4/5/2026 08:38</t>
+          <t>4/5/2026 08:45</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>4/5/2026 08:38</t>
+          <t>4/5/2026 08:47</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>4/5/2026 09:08</t>
+          <t>4/5/2026 09:17</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M73" t="n">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="74">
@@ -6092,48 +6092,48 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>4/5/2026 11:06</t>
+          <t>4/5/2026 11:04</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
+          <t>4/5/2026 11:08</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>4/5/2026 11:08</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
           <t>4/5/2026 11:10</t>
         </is>
       </c>
-      <c r="F74" t="n">
-        <v>2</v>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>4/5/2026 11:20</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>4/5/2026 11:22</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>4/5/2026 11:22</t>
+          <t>4/5/2026 11:10</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>4/5/2026 11:43</t>
+          <t>4/5/2026 11:31</t>
         </is>
       </c>
       <c r="L74" t="n">
         <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="N74" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -6152,48 +6152,48 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>4/5/2026 08:05</t>
+          <t>4/5/2026 08:15</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>4/5/2026 08:14</t>
+          <t>4/5/2026 08:24</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>4/5/2026 08:14</t>
+          <t>4/5/2026 08:31</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>4/5/2026 08:16</t>
+          <t>4/5/2026 08:33</t>
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>4/5/2026 08:16</t>
+          <t>4/5/2026 08:43</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>4/5/2026 08:36</t>
+          <t>4/5/2026 09:03</t>
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M75" t="n">
-        <v>31</v>
+        <v>58</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="76">
@@ -6285,35 +6285,35 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>4/5/2026 11:14</t>
+          <t>4/5/2026 11:17</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>4/5/2026 11:16</t>
+          <t>4/5/2026 11:19</t>
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>4/5/2026 11:16</t>
+          <t>4/5/2026 11:29</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>4/5/2026 11:53</t>
+          <t>4/5/2026 12:06</t>
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M77" t="n">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="78">
@@ -6358,22 +6358,22 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>4/5/2026 06:20</t>
+          <t>4/5/2026 06:21</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>4/5/2026 06:22</t>
+          <t>4/5/2026 06:23</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M78" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -6392,48 +6392,48 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>4/5/2026 07:08</t>
+          <t>4/5/2026 07:18</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>4/5/2026 07:20</t>
+          <t>4/5/2026 07:30</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>4/5/2026 07:20</t>
+          <t>4/5/2026 07:37</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>4/5/2026 07:21</t>
+          <t>4/5/2026 07:38</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>4/5/2026 07:21</t>
+          <t>4/5/2026 07:48</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>4/5/2026 07:28</t>
+          <t>4/5/2026 07:55</t>
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M79" t="n">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="80">
@@ -6452,48 +6452,48 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>4/5/2026 09:09</t>
+          <t>4/5/2026 09:19</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>4/5/2026 09:18</t>
+          <t>4/5/2026 09:28</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>4/5/2026 09:18</t>
+          <t>4/5/2026 09:31</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>4/5/2026 09:20</t>
+          <t>4/5/2026 09:33</t>
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>4/5/2026 09:20</t>
+          <t>4/5/2026 09:40</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>4/5/2026 09:29</t>
+          <t>4/5/2026 09:49</t>
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M80" t="n">
+        <v>40</v>
+      </c>
+      <c r="N80" t="n">
         <v>20</v>
-      </c>
-      <c r="N80" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -6538,22 +6538,22 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>4/5/2026 09:13</t>
+          <t>4/5/2026 09:23</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>4/5/2026 09:21</t>
+          <t>4/5/2026 09:31</t>
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M81" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="82">
@@ -6572,48 +6572,48 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>4/5/2026 09:16</t>
+          <t>4/5/2026 09:22</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>4/5/2026 09:34</t>
+          <t>4/5/2026 09:40</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>4/5/2026 09:34</t>
+          <t>4/5/2026 09:47</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>4/5/2026 09:36</t>
+          <t>4/5/2026 09:49</t>
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>4/5/2026 09:36</t>
+          <t>4/5/2026 09:49</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>4/5/2026 09:56</t>
+          <t>4/5/2026 10:09</t>
         </is>
       </c>
       <c r="L82" t="n">
         <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="83">
@@ -6632,48 +6632,48 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
+          <t>4/5/2026 11:02</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>4/5/2026 11:16</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>4/5/2026 11:16</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
           <t>4/5/2026 11:17</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>4/5/2026 11:31</t>
-        </is>
-      </c>
-      <c r="F83" t="n">
-        <v>15</v>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>4/5/2026 11:41</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>4/5/2026 11:42</t>
-        </is>
-      </c>
       <c r="I83" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>4/5/2026 11:43</t>
+          <t>4/5/2026 11:17</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>4/5/2026 12:06</t>
+          <t>4/5/2026 11:40</t>
         </is>
       </c>
       <c r="L83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>64</v>
+        <v>38</v>
       </c>
       <c r="N83" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -6692,48 +6692,48 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>4/5/2026 11:41</t>
+          <t>4/5/2026 11:37</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>4/5/2026 11:53</t>
+          <t>4/5/2026 11:49</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>4/5/2026 12:02</t>
+          <t>4/5/2026 11:49</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>4/5/2026 12:05</t>
+          <t>4/5/2026 11:52</t>
         </is>
       </c>
       <c r="I84" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>4/5/2026 12:10</t>
+          <t>4/5/2026 11:52</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>4/5/2026 12:40</t>
+          <t>4/5/2026 12:22</t>
         </is>
       </c>
       <c r="L84" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="N84" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -6778,22 +6778,22 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
+          <t>4/5/2026 09:05</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
           <t>4/5/2026 09:08</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:11</t>
-        </is>
-      </c>
       <c r="L85" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M85" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="N85" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86">
@@ -6812,48 +6812,48 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>4/5/2026 09:00</t>
+          <t>4/5/2026 08:55</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>4/5/2026 09:08</t>
+          <t>4/5/2026 09:03</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>4/5/2026 09:18</t>
+          <t>4/5/2026 09:10</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>4/5/2026 09:20</t>
+          <t>4/5/2026 09:12</t>
         </is>
       </c>
       <c r="I86" t="n">
+        <v>7</v>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>4/5/2026 09:22</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>4/5/2026 10:15</t>
+        </is>
+      </c>
+      <c r="L86" t="n">
         <v>10</v>
       </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:21</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>4/5/2026 10:14</t>
-        </is>
-      </c>
-      <c r="L86" t="n">
-        <v>1</v>
-      </c>
       <c r="M86" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="N86" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="87">
@@ -6898,22 +6898,22 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>4/5/2026 12:07</t>
+          <t>4/5/2026 12:11</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>4/5/2026 12:53</t>
+          <t>4/5/2026 12:57</t>
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M87" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="88">
@@ -6932,48 +6932,48 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>4/5/2026 06:00</t>
+          <t>4/5/2026 06:10</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>4/5/2026 06:02</t>
+          <t>4/5/2026 06:12</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>4/5/2026 06:02</t>
+          <t>4/5/2026 06:19</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>4/5/2026 06:03</t>
+          <t>4/5/2026 06:20</t>
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>4/5/2026 06:03</t>
+          <t>4/5/2026 06:30</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>4/5/2026 06:05</t>
+          <t>4/5/2026 06:32</t>
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M88" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="89">
@@ -6992,48 +6992,48 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>4/5/2026 08:53</t>
+          <t>4/5/2026 09:03</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>4/5/2026 08:55</t>
+          <t>4/5/2026 09:05</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>4/5/2026 08:55</t>
+          <t>4/5/2026 09:11</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>4/5/2026 08:56</t>
+          <t>4/5/2026 09:12</t>
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>4/5/2026 08:56</t>
+          <t>4/5/2026 09:22</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>4/5/2026 09:02</t>
+          <t>4/5/2026 09:28</t>
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M89" t="n">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
     </row>
     <row r="90">
@@ -7078,22 +7078,22 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>4/5/2026 09:11</t>
+          <t>4/5/2026 09:12</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>4/5/2026 09:12</t>
+          <t>4/5/2026 09:13</t>
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M90" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
@@ -7138,22 +7138,22 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>4/5/2026 07:29</t>
+          <t>4/5/2026 07:30</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>4/5/2026 07:45</t>
+          <t>4/5/2026 07:46</t>
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M91" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
@@ -7172,25 +7172,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>4/5/2026 06:48</t>
+          <t>4/5/2026 06:55</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>4/5/2026 06:58</t>
+          <t>4/5/2026 07:05</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>4/5/2026 06:58</t>
+          <t>4/5/2026 07:05</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>4/5/2026 07:00</t>
+          <t>4/5/2026 07:07</t>
         </is>
       </c>
       <c r="I92" t="n">
@@ -7198,22 +7198,22 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>4/5/2026 07:00</t>
+          <t>4/5/2026 07:07</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>4/5/2026 07:23</t>
+          <t>4/5/2026 07:30</t>
         </is>
       </c>
       <c r="L92" t="n">
         <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="93">
@@ -7318,22 +7318,22 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>4/5/2026 08:38</t>
+          <t>4/5/2026 08:46</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>4/5/2026 09:08</t>
+          <t>4/5/2026 09:16</t>
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M94" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="95">
@@ -7352,48 +7352,48 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>4/5/2026 11:08</t>
+          <t>4/5/2026 11:04</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>4/5/2026 11:13</t>
+          <t>4/5/2026 11:09</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>4/5/2026 11:23</t>
+          <t>4/5/2026 11:09</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>4/5/2026 11:25</t>
+          <t>4/5/2026 11:11</t>
         </is>
       </c>
       <c r="I95" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>4/5/2026 11:25</t>
+          <t>4/5/2026 11:11</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>4/5/2026 11:46</t>
+          <t>4/5/2026 11:32</t>
         </is>
       </c>
       <c r="L95" t="n">
         <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="N95" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -7412,48 +7412,48 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>4/5/2026 08:05</t>
+          <t>4/5/2026 08:15</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>4/5/2026 08:14</t>
+          <t>4/5/2026 08:24</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>4/5/2026 08:14</t>
+          <t>4/5/2026 08:31</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>4/5/2026 08:15</t>
+          <t>4/5/2026 08:32</t>
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>4/5/2026 08:15</t>
+          <t>4/5/2026 08:42</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>4/5/2026 08:35</t>
+          <t>4/5/2026 09:02</t>
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M96" t="n">
-        <v>30</v>
+        <v>57</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="97">
@@ -7472,25 +7472,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>4/5/2026 11:14</t>
+          <t>4/5/2026 11:13</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>4/5/2026 11:26</t>
+          <t>4/5/2026 11:25</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>4/5/2026 11:26</t>
+          <t>4/5/2026 11:25</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>4/5/2026 11:29</t>
+          <t>4/5/2026 11:28</t>
         </is>
       </c>
       <c r="I97" t="n">
@@ -7498,22 +7498,22 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>4/5/2026 11:29</t>
+          <t>4/5/2026 11:28</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>4/5/2026 11:49</t>
+          <t>4/5/2026 11:48</t>
         </is>
       </c>
       <c r="L97" t="n">
         <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -7558,22 +7558,22 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>4/5/2026 08:49</t>
+          <t>4/5/2026 08:54</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>4/5/2026 09:17</t>
+          <t>4/5/2026 09:22</t>
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M98" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="99">
@@ -7618,22 +7618,22 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>4/5/2026 06:20</t>
+          <t>4/5/2026 06:21</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>4/5/2026 06:22</t>
+          <t>4/5/2026 06:23</t>
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M99" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100">
@@ -7652,48 +7652,48 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
+          <t>4/5/2026 10:31</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>4/5/2026 10:44</t>
+        </is>
+      </c>
+      <c r="F100" t="n">
+        <v>0</v>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>4/5/2026 10:44</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
           <t>4/5/2026 10:46</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>4/5/2026 10:59</t>
-        </is>
-      </c>
-      <c r="F100" t="n">
-        <v>15</v>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>4/5/2026 10:59</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>4/5/2026 11:01</t>
-        </is>
-      </c>
       <c r="I100" t="n">
         <v>0</v>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>4/5/2026 11:02</t>
+          <t>4/5/2026 10:46</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>4/5/2026 11:11</t>
+          <t>4/5/2026 10:55</t>
         </is>
       </c>
       <c r="L100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M100" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="N100" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -7712,48 +7712,48 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>4/5/2026 09:09</t>
+          <t>4/5/2026 09:19</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>4/5/2026 09:17</t>
+          <t>4/5/2026 09:27</t>
         </is>
       </c>
       <c r="F101" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>4/5/2026 09:17</t>
+          <t>4/5/2026 09:34</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>4/5/2026 09:18</t>
+          <t>4/5/2026 09:35</t>
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>4/5/2026 09:18</t>
+          <t>4/5/2026 09:40</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>4/5/2026 09:27</t>
+          <t>4/5/2026 09:49</t>
         </is>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M101" t="n">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="102">
@@ -7785,35 +7785,35 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>4/5/2026 09:11</t>
+          <t>4/5/2026 09:18</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>4/5/2026 09:13</t>
+          <t>4/5/2026 09:20</t>
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>4/5/2026 09:13</t>
+          <t>4/5/2026 09:28</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>4/5/2026 09:21</t>
+          <t>4/5/2026 09:36</t>
         </is>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M102" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="103">
@@ -7832,25 +7832,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>4/5/2026 09:16</t>
+          <t>4/5/2026 09:17</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>4/5/2026 09:36</t>
+          <t>4/5/2026 09:37</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>4/5/2026 09:36</t>
+          <t>4/5/2026 09:37</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>4/5/2026 09:38</t>
+          <t>4/5/2026 09:39</t>
         </is>
       </c>
       <c r="I103" t="n">
@@ -7858,22 +7858,22 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>4/5/2026 09:38</t>
+          <t>4/5/2026 09:49</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>4/5/2026 09:58</t>
+          <t>4/5/2026 10:09</t>
         </is>
       </c>
       <c r="L103" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M103" t="n">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="104">
@@ -7892,48 +7892,48 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>4/5/2026 09:58</t>
+          <t>4/5/2026 10:06</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>4/5/2026 10:13</t>
+          <t>4/5/2026 10:21</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>4/5/2026 10:13</t>
+          <t>4/5/2026 10:28</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>4/5/2026 10:15</t>
+          <t>4/5/2026 10:30</t>
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>4/5/2026 10:15</t>
+          <t>4/5/2026 10:37</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>4/5/2026 10:42</t>
+          <t>4/5/2026 11:04</t>
         </is>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M104" t="n">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="105">
@@ -7952,48 +7952,48 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>4/5/2026 08:36</t>
+          <t>4/5/2026 08:42</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>4/5/2026 08:51</t>
+          <t>4/5/2026 08:57</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>4/5/2026 08:51</t>
+          <t>4/5/2026 09:04</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>4/5/2026 08:53</t>
+          <t>4/5/2026 09:06</t>
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>4/5/2026 09:02</t>
+          <t>4/5/2026 09:16</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>4/5/2026 09:35</t>
+          <t>4/5/2026 09:49</t>
         </is>
       </c>
       <c r="L105" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M105" t="n">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="N105" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
     </row>
     <row r="106">
@@ -8012,48 +8012,48 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>4/5/2026 08:56</t>
+          <t>4/5/2026 08:57</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>4/5/2026 09:02</t>
+          <t>4/5/2026 09:03</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>4/5/2026 09:02</t>
+          <t>4/5/2026 09:04</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>4/5/2026 09:03</t>
+          <t>4/5/2026 09:05</t>
         </is>
       </c>
       <c r="I106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J106" t="inlineStr">
         <is>
+          <t>4/5/2026 09:05</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
           <t>4/5/2026 09:08</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:11</t>
-        </is>
-      </c>
       <c r="L106" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="N106" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/Thesis_TSSP_NEW_M1_Results_5_Scenarios.xlsx
+++ b/Thesis_TSSP_NEW_M1_Results_5_Scenarios.xlsx
@@ -1372,7 +1372,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>29.2020 sec</t>
+          <t>28.7790 sec</t>
         </is>
       </c>
     </row>
